--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB MORVEDRE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB MORVEDRE.xlsx
@@ -565,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>40.7578</v>
+        <v>24.0402</v>
       </c>
       <c r="E2" t="n">
-        <v>39.5131</v>
+        <v>22.8377</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2451</v>
+        <v>1.2023</v>
       </c>
       <c r="G2" t="n">
         <v>9.542199999999999</v>
@@ -610,13 +610,13 @@
         <v>29.8709</v>
       </c>
       <c r="S2" t="n">
-        <v>30.6492</v>
+        <v>13.9316</v>
       </c>
       <c r="T2" t="n">
-        <v>26.579</v>
+        <v>9.904</v>
       </c>
       <c r="U2" t="n">
-        <v>4.07</v>
+        <v>4.0275</v>
       </c>
       <c r="V2" t="n">
         <v>14.3106</v>
@@ -643,13 +643,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>11.5038</v>
+        <v>14.5338</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0196</v>
+        <v>5.633099999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>9.4842</v>
+        <v>8.9009</v>
       </c>
       <c r="G3" t="n">
         <v>6.357100000000001</v>
@@ -688,13 +688,13 @@
         <v>15.2103</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0832</v>
+        <v>4.1135</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.9131</v>
+        <v>0.7004000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>3.9964</v>
+        <v>3.413</v>
       </c>
       <c r="V3" t="n">
         <v>5.346399999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MERENCIO FERRER</t>
+          <t>J. SEGARRA SARIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6887999999999993</v>
+        <v>0.249</v>
       </c>
       <c r="E5" t="n">
-        <v>8.213799999999999</v>
+        <v>1.3114</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.524900000000001</v>
+        <v>-1.0624</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1602</v>
+        <v>0.5386</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1366</v>
+        <v>0.5581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.01929999999999998</v>
       </c>
       <c r="J5" t="n">
-        <v>9.76</v>
+        <v>1.6089</v>
       </c>
       <c r="K5" t="n">
-        <v>6.6343</v>
+        <v>1.2755</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1256</v>
+        <v>0.3334</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.9201</v>
+        <v>-1.0702</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.770899999999999</v>
+        <v>-0.7175</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1491</v>
+        <v>-0.3528</v>
       </c>
       <c r="P5" t="n">
-        <v>1.466</v>
+        <v>0.3666</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.8643</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>7.3303</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9376</v>
+        <v>-0.0227</v>
       </c>
       <c r="T5" t="n">
-        <v>3.0304</v>
+        <v>-0.0147</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09270000000000006</v>
+        <v>-0.008000000000000007</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5548</v>
+        <v>-0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2878</v>
+        <v>0.6335</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.8425</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>M. RODRIGUEZ MERINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03890000000000038</v>
+        <v>-0.4367000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9699</v>
+        <v>-1.3251</v>
       </c>
       <c r="F6" t="n">
-        <v>-24.9309</v>
+        <v>0.8883000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-24.7047</v>
+        <v>-1.5901</v>
       </c>
       <c r="H6" t="n">
-        <v>-18.1909</v>
+        <v>-0.02910000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.5139</v>
+        <v>-1.561</v>
       </c>
       <c r="J6" t="n">
-        <v>17.7893</v>
+        <v>-1.1321</v>
       </c>
       <c r="K6" t="n">
-        <v>13.2694</v>
+        <v>0.1084</v>
       </c>
       <c r="L6" t="n">
-        <v>4.519599999999999</v>
+        <v>-1.2404</v>
       </c>
       <c r="M6" t="n">
-        <v>-42.4941</v>
+        <v>-0.458</v>
       </c>
       <c r="N6" t="n">
-        <v>-31.4604</v>
+        <v>-0.1374</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.0334</v>
+        <v>-0.3206</v>
       </c>
       <c r="P6" t="n">
-        <v>8.9793</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-26.0226</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>35.0021</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>18.6219</v>
+        <v>0.3024</v>
       </c>
       <c r="T6" t="n">
-        <v>7.6656</v>
+        <v>-0.193</v>
       </c>
       <c r="U6" t="n">
-        <v>10.956</v>
+        <v>0.4955000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.8578</v>
+        <v>0.3012</v>
       </c>
       <c r="W6" t="n">
-        <v>25.5371</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-28.3952</v>
+        <v>0.3012</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SEGARRA SARIO</t>
+          <t>L. BARCOS PERALTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.034</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7756000000000001</v>
+        <v>6.5566</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4092</v>
+        <v>-7.590399999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5386</v>
+        <v>-9.655700000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5581</v>
+        <v>-7.9165</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01929999999999998</v>
+        <v>-1.739</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6089</v>
+        <v>4.298</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2755</v>
+        <v>2.7014</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3334</v>
+        <v>1.5964</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0702</v>
+        <v>-13.9536</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7175</v>
+        <v>-10.6182</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3528</v>
+        <v>-3.3354</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3666</v>
+        <v>2.7487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-10.0792</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2828</v>
+        <v>12.828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9053</v>
+        <v>-2.6636</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5506</v>
+        <v>-1.0176</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3547</v>
+        <v>-1.6461</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6335</v>
+        <v>8.5364</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6335</v>
+        <v>13.3552</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>-4.818700000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MERINO</t>
+          <t>J. MERENCIO FERRER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7830999999999999</v>
+        <v>-1.668</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5724</v>
+        <v>6.7855</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7893</v>
+        <v>-8.4535</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5901</v>
+        <v>-1.1602</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02910000000000001</v>
+        <v>-2.1366</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.561</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1321</v>
+        <v>9.76</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1084</v>
+        <v>6.6343</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2404</v>
+        <v>3.1256</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.458</v>
+        <v>-10.9201</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1374</v>
+        <v>-8.770899999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3206</v>
+        <v>-2.1491</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>1.466</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.8643</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5498</v>
+        <v>7.3303</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.044</v>
+        <v>0.5809</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4405</v>
+        <v>1.6019</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3963</v>
+        <v>-1.0209</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3012</v>
+        <v>-2.5548</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3012</v>
+        <v>-3.8425</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BARCOS PERALTA</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6617</v>
+        <v>-1.976799999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>7.283799999999999</v>
+        <v>16.6412</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.945599999999999</v>
+        <v>-18.6179</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.655700000000001</v>
+        <v>1.921800000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.9165</v>
+        <v>-17.8311</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.739</v>
+        <v>19.7523</v>
       </c>
       <c r="J9" t="n">
-        <v>4.298</v>
+        <v>41.1229</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7014</v>
+        <v>14.1517</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5964</v>
+        <v>26.9714</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.9536</v>
+        <v>-39.2018</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.6182</v>
+        <v>-31.9824</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.3354</v>
+        <v>-7.218900000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7487</v>
+        <v>-2.5655</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.0792</v>
+        <v>-40.8665</v>
       </c>
       <c r="R9" t="n">
-        <v>12.828</v>
+        <v>38.3006</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2913</v>
+        <v>-3.3015</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2902</v>
+        <v>-2.4124</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.0013</v>
+        <v>-0.8891000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5364</v>
+        <v>1.9691</v>
       </c>
       <c r="W9" t="n">
-        <v>13.3552</v>
+        <v>18.7971</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.818700000000001</v>
+        <v>-16.8279</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.566800000000001</v>
+        <v>-3.986899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9963</v>
+        <v>-2.5155</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5704</v>
+        <v>-1.4714</v>
       </c>
       <c r="G10" t="n">
         <v>-5.3282</v>
@@ -1234,13 +1234,13 @@
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02839999999999998</v>
+        <v>0.6082000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8092</v>
+        <v>-0.3283</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8375</v>
+        <v>0.9367000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>9.999999999987796e-05</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. GARCIA MARAVILLA</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9612</v>
+        <v>-4.087000000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8929</v>
+        <v>14.0948</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0683</v>
+        <v>-18.1818</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5666</v>
+        <v>-20.4021</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7394</v>
+        <v>-21.7161</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8270999999999999</v>
+        <v>1.3142</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2058</v>
+        <v>16.4404</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07100000000000006</v>
+        <v>8.068399999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1347999999999999</v>
+        <v>8.371700000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7724</v>
+        <v>-36.8428</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8105</v>
+        <v>-29.7849</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9619000000000001</v>
+        <v>-7.058</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5497</v>
+        <v>-13.7443</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0159</v>
+        <v>-43.6154</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4661</v>
+        <v>29.8708</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5125</v>
+        <v>-4.6223</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.083</v>
+        <v>-3.5422</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4297</v>
+        <v>-1.0803</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3323</v>
+        <v>34.6821</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>44.8116</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3323</v>
+        <v>-10.1293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.354399999999999</v>
+        <v>-4.1675</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8898000000000001</v>
+        <v>-8.7128</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.2445</v>
+        <v>4.5455</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.1639</v>
+        <v>-6.5681</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9651</v>
+        <v>-6.7539</v>
       </c>
       <c r="I12" t="n">
-        <v>-13.1287</v>
+        <v>0.1857999999999996</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6161</v>
+        <v>-4.814299999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>22.0141</v>
+        <v>-2.8216</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.3979</v>
+        <v>-1.9927</v>
       </c>
       <c r="M12" t="n">
-        <v>-27.7796</v>
+        <v>-1.7539</v>
       </c>
       <c r="N12" t="n">
-        <v>-20.049</v>
+        <v>-3.9324</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.730799999999999</v>
+        <v>2.1787</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2828</v>
+        <v>0.1832</v>
       </c>
       <c r="Q12" t="n">
-        <v>-28.7716</v>
+        <v>-5.6811</v>
       </c>
       <c r="R12" t="n">
-        <v>27.4884</v>
+        <v>5.8643</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0075</v>
+        <v>3.1832</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2447</v>
+        <v>1.4607</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2526</v>
+        <v>1.7228</v>
       </c>
       <c r="V12" t="n">
-        <v>3.0842</v>
+        <v>-0.9658999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>14.2897</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.2056</v>
+        <v>-1.2878</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GOMEZ MONTES</t>
+          <t>P. GARCIA MARAVILLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6663</v>
+        <v>-4.5476</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7423</v>
+        <v>-2.5083</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9241</v>
+        <v>-2.0391</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.465</v>
+        <v>-2.5666</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5445000000000002</v>
+        <v>-1.7394</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.9205</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7521</v>
+        <v>0.2058</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8857</v>
+        <v>0.07100000000000006</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.6378</v>
+        <v>0.1347999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.7128</v>
+        <v>-2.7724</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.4301</v>
+        <v>-1.8105</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2826</v>
+        <v>-0.9619000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.466</v>
+        <v>-0.5497</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>-2.0159</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2985</v>
+        <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3351</v>
+        <v>-1.0988</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1576</v>
+        <v>-0.6983</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1776</v>
+        <v>-0.4004</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3324</v>
+        <v>-0.3323</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3324</v>
+        <v>-0.3323</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.036300000000001</v>
+        <v>-4.601399999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.0073</v>
+        <v>2.0996</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9712</v>
+        <v>-6.700799999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.5681</v>
+        <v>-11.1639</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.7539</v>
+        <v>1.9651</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1857999999999996</v>
+        <v>-13.1287</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.814299999999999</v>
+        <v>16.6161</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.8216</v>
+        <v>22.0141</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.9927</v>
+        <v>-5.3979</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7539</v>
+        <v>-27.7796</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.9324</v>
+        <v>-20.049</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1787</v>
+        <v>-7.730799999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1832</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.6811</v>
+        <v>-28.7716</v>
       </c>
       <c r="R14" t="n">
-        <v>5.8643</v>
+        <v>27.4884</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3145000000000001</v>
+        <v>4.7611</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8340000000000001</v>
+        <v>-0.03479999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1486</v>
+        <v>4.796</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9658999999999999</v>
+        <v>3.0842</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3219</v>
+        <v>14.2897</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2878</v>
+        <v>-11.2056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>J. GOMEZ MONTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.5441</v>
+        <v>-5.3671</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8027</v>
+        <v>-3.918</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.3468</v>
+        <v>-1.449</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.010899999999999</v>
+        <v>-5.465</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.5607</v>
+        <v>-0.5445000000000002</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4504</v>
+        <v>-4.9205</v>
       </c>
       <c r="J15" t="n">
-        <v>9.6366</v>
+        <v>-1.7521</v>
       </c>
       <c r="K15" t="n">
-        <v>8.1347</v>
+        <v>1.8857</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5018</v>
+        <v>-3.6378</v>
       </c>
       <c r="M15" t="n">
-        <v>-18.6472</v>
+        <v>-3.7128</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.6953</v>
+        <v>-2.4301</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.9519</v>
+        <v>-1.2826</v>
       </c>
       <c r="P15" t="n">
-        <v>6.230899999999999</v>
+        <v>1.466</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.5612</v>
+        <v>-1.8326</v>
       </c>
       <c r="R15" t="n">
-        <v>19.7918</v>
+        <v>3.2985</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5901999999999998</v>
+        <v>-1.0358</v>
       </c>
       <c r="T15" t="n">
-        <v>4.8329</v>
+        <v>-0.3333</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.2425</v>
+        <v>-0.7025</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.3542</v>
+        <v>-0.3324</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8945</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.248999999999999</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.085699999999999</v>
+        <v>-7.413499999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4745999999999996</v>
+        <v>1.9461</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.6112</v>
+        <v>-9.3598</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.4329</v>
+        <v>-9.010899999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.9345</v>
+        <v>-7.5607</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5014000000000003</v>
+        <v>-1.4504</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2931000000000002</v>
+        <v>9.6366</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7489</v>
+        <v>8.1347</v>
       </c>
       <c r="L16" t="n">
-        <v>2.042</v>
+        <v>1.5018</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.726100000000001</v>
+        <v>-18.6472</v>
       </c>
       <c r="N16" t="n">
-        <v>-6.1856</v>
+        <v>-15.6953</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5407</v>
+        <v>-2.9519</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7327999999999999</v>
+        <v>6.230899999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.7805</v>
+        <v>-13.5612</v>
       </c>
       <c r="R16" t="n">
-        <v>6.0477</v>
+        <v>19.7918</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1897</v>
+        <v>0.7206999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>3.78</v>
+        <v>1.9761</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5903</v>
+        <v>-1.2555</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.1092</v>
+        <v>-5.3542</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2328</v>
+        <v>3.8945</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.3421</v>
+        <v>-9.248999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-10.9406</v>
+        <v>-10.7334</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.0181</v>
+        <v>19.6827</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.922499999999999</v>
+        <v>-30.4159</v>
       </c>
       <c r="G17" t="n">
-        <v>-18.1442</v>
+        <v>-24.7047</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.9151</v>
+        <v>-18.1909</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.2294</v>
+        <v>-6.5139</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6076000000000008</v>
+        <v>17.7893</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8401000000000004</v>
+        <v>13.2694</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2326000000000001</v>
+        <v>4.519599999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-18.7521</v>
+        <v>-42.4941</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.7551</v>
+        <v>-31.4604</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.9968</v>
+        <v>-11.0334</v>
       </c>
       <c r="P17" t="n">
-        <v>3.8483</v>
+        <v>8.9793</v>
       </c>
       <c r="Q17" t="n">
-        <v>-12.2785</v>
+        <v>-26.0226</v>
       </c>
       <c r="R17" t="n">
-        <v>16.1267</v>
+        <v>35.0021</v>
       </c>
       <c r="S17" t="n">
-        <v>5.276800000000001</v>
+        <v>7.8493</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8101</v>
+        <v>2.3787</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4666</v>
+        <v>5.470800000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.9212</v>
+        <v>-2.8578</v>
       </c>
       <c r="W17" t="n">
-        <v>3.8424</v>
+        <v>25.5371</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.7637</v>
+        <v>-28.3952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-14.5193</v>
+        <v>-10.8464</v>
       </c>
       <c r="E18" t="n">
-        <v>8.494400000000001</v>
+        <v>12.0564</v>
       </c>
       <c r="F18" t="n">
-        <v>-23.0142</v>
+        <v>-22.9031</v>
       </c>
       <c r="G18" t="n">
-        <v>1.921800000000001</v>
+        <v>9.988099999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-17.8311</v>
+        <v>-1.881799999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>19.7523</v>
+        <v>11.8694</v>
       </c>
       <c r="J18" t="n">
-        <v>41.1229</v>
+        <v>51.767</v>
       </c>
       <c r="K18" t="n">
-        <v>14.1517</v>
+        <v>26.5231</v>
       </c>
       <c r="L18" t="n">
-        <v>26.9714</v>
+        <v>25.244</v>
       </c>
       <c r="M18" t="n">
-        <v>-39.2018</v>
+        <v>-41.7791</v>
       </c>
       <c r="N18" t="n">
-        <v>-31.9824</v>
+        <v>-28.4051</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.218900000000001</v>
+        <v>-13.374</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5655</v>
+        <v>-21.6243</v>
       </c>
       <c r="Q18" t="n">
-        <v>-40.8665</v>
+        <v>-62.1243</v>
       </c>
       <c r="R18" t="n">
-        <v>38.3006</v>
+        <v>40.4999</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.8442</v>
+        <v>1.2028</v>
       </c>
       <c r="T18" t="n">
-        <v>-10.5592</v>
+        <v>-1.7839</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.284899999999999</v>
+        <v>2.9869</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9691</v>
+        <v>-0.4136000000000002</v>
       </c>
       <c r="W18" t="n">
-        <v>18.7971</v>
+        <v>24.1971</v>
       </c>
       <c r="X18" t="n">
-        <v>-16.8279</v>
+        <v>-24.6108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-17.9346</v>
+        <v>-11.6494</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.0587</v>
+        <v>-3.4274</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.8762</v>
+        <v>-8.222</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0146</v>
+        <v>-7.4329</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.0763</v>
+        <v>-7.9345</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0616</v>
+        <v>0.5014000000000003</v>
       </c>
       <c r="J19" t="n">
-        <v>9.0989</v>
+        <v>0.2931000000000002</v>
       </c>
       <c r="K19" t="n">
-        <v>5.0219</v>
+        <v>-1.7489</v>
       </c>
       <c r="L19" t="n">
-        <v>4.0771</v>
+        <v>2.042</v>
       </c>
       <c r="M19" t="n">
-        <v>-12.1136</v>
+        <v>-7.726100000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-9.098100000000001</v>
+        <v>-6.1856</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.0156</v>
+        <v>-1.5407</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5497</v>
+        <v>-0.7327999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-15.7602</v>
+        <v>-6.7805</v>
       </c>
       <c r="R19" t="n">
-        <v>16.3099</v>
+        <v>6.0477</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.4598</v>
+        <v>-0.3744999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.6408</v>
+        <v>0.8271000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.819</v>
+        <v>-1.2013</v>
       </c>
       <c r="V19" t="n">
-        <v>-7.01</v>
+        <v>-3.1092</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2432</v>
+        <v>2.2328</v>
       </c>
       <c r="X19" t="n">
-        <v>-9.2531</v>
+        <v>-5.3421</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>-20.0161</v>
+        <v>-11.7754</v>
       </c>
       <c r="E20" t="n">
-        <v>2.705899999999999</v>
+        <v>-5.593799999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-22.7223</v>
+        <v>-6.181399999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.4021</v>
+        <v>-3.0146</v>
       </c>
       <c r="H20" t="n">
-        <v>-21.7161</v>
+        <v>-4.0763</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3142</v>
+        <v>1.0616</v>
       </c>
       <c r="J20" t="n">
-        <v>16.4404</v>
+        <v>9.0989</v>
       </c>
       <c r="K20" t="n">
-        <v>8.068399999999999</v>
+        <v>5.0219</v>
       </c>
       <c r="L20" t="n">
-        <v>8.371700000000001</v>
+        <v>4.0771</v>
       </c>
       <c r="M20" t="n">
-        <v>-36.8428</v>
+        <v>-12.1136</v>
       </c>
       <c r="N20" t="n">
-        <v>-29.7849</v>
+        <v>-9.098100000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.058</v>
+        <v>-3.0156</v>
       </c>
       <c r="P20" t="n">
-        <v>-13.7443</v>
+        <v>0.5497</v>
       </c>
       <c r="Q20" t="n">
-        <v>-43.6154</v>
+        <v>-15.7602</v>
       </c>
       <c r="R20" t="n">
-        <v>29.8708</v>
+        <v>16.3099</v>
       </c>
       <c r="S20" t="n">
-        <v>-20.5518</v>
+        <v>-2.3003</v>
       </c>
       <c r="T20" t="n">
-        <v>-14.9309</v>
+        <v>-1.1758</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.6207</v>
+        <v>-1.1243</v>
       </c>
       <c r="V20" t="n">
-        <v>34.6821</v>
+        <v>-7.01</v>
       </c>
       <c r="W20" t="n">
-        <v>44.8116</v>
+        <v>2.2432</v>
       </c>
       <c r="X20" t="n">
-        <v>-10.1293</v>
+        <v>-9.2531</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>-23.1812</v>
+        <v>-13.0485</v>
       </c>
       <c r="E21" t="n">
-        <v>4.307499999999999</v>
+        <v>-6.1189</v>
       </c>
       <c r="F21" t="n">
-        <v>-27.4888</v>
+        <v>-6.9298</v>
       </c>
       <c r="G21" t="n">
-        <v>9.988099999999999</v>
+        <v>-18.1442</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.881799999999999</v>
+        <v>-11.9151</v>
       </c>
       <c r="I21" t="n">
-        <v>11.8694</v>
+        <v>-6.2294</v>
       </c>
       <c r="J21" t="n">
-        <v>51.767</v>
+        <v>0.6076000000000008</v>
       </c>
       <c r="K21" t="n">
-        <v>26.5231</v>
+        <v>0.8401000000000004</v>
       </c>
       <c r="L21" t="n">
-        <v>25.244</v>
+        <v>-0.2326000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-41.7791</v>
+        <v>-18.7521</v>
       </c>
       <c r="N21" t="n">
-        <v>-28.4051</v>
+        <v>-12.7551</v>
       </c>
       <c r="O21" t="n">
-        <v>-13.374</v>
+        <v>-5.9968</v>
       </c>
       <c r="P21" t="n">
-        <v>-21.6243</v>
+        <v>3.8483</v>
       </c>
       <c r="Q21" t="n">
-        <v>-62.1243</v>
+        <v>-12.2785</v>
       </c>
       <c r="R21" t="n">
-        <v>40.4999</v>
+        <v>16.1267</v>
       </c>
       <c r="S21" t="n">
-        <v>-11.1316</v>
+        <v>3.1688</v>
       </c>
       <c r="T21" t="n">
-        <v>-9.532300000000001</v>
+        <v>1.7095</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5986</v>
+        <v>1.4594</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4136000000000002</v>
+        <v>-1.9212</v>
       </c>
       <c r="W21" t="n">
-        <v>24.1971</v>
+        <v>3.8424</v>
       </c>
       <c r="X21" t="n">
-        <v>-24.6108</v>
+        <v>-5.7637</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-23.5521</v>
+        <v>-25.1721</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.1283</v>
+        <v>-13.2812</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.4237</v>
+        <v>-11.8909</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.348899999999998</v>
+        <v>-18.6521</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.028</v>
+        <v>-15.1091</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.3208</v>
+        <v>-3.542800000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>19.3135</v>
+        <v>4.0074</v>
       </c>
       <c r="K22" t="n">
-        <v>17.1217</v>
+        <v>3.3459</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1917</v>
+        <v>0.6616</v>
       </c>
       <c r="M22" t="n">
-        <v>-26.6621</v>
+        <v>-22.6596</v>
       </c>
       <c r="N22" t="n">
-        <v>-20.1495</v>
+        <v>-18.4555</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.512700000000001</v>
+        <v>-4.204</v>
       </c>
       <c r="P22" t="n">
-        <v>-5.131499999999999</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q22" t="n">
-        <v>-36.285</v>
+        <v>-27.6721</v>
       </c>
       <c r="R22" t="n">
-        <v>31.1536</v>
+        <v>25.4727</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2674</v>
+        <v>-1.4632</v>
       </c>
       <c r="T22" t="n">
-        <v>5.6422</v>
+        <v>-0.843</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.375</v>
+        <v>-0.6198</v>
       </c>
       <c r="V22" t="n">
-        <v>-14.3395</v>
+        <v>-2.8578</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7993999999999997</v>
+        <v>11.2265</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.5401</v>
+        <v>-14.0843</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>-29.6189</v>
+        <v>-25.3558</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.2189</v>
+        <v>-15.9459</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.4003</v>
+        <v>-9.4102</v>
       </c>
       <c r="G23" t="n">
-        <v>-18.6521</v>
+        <v>-7.348899999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>-15.1091</v>
+        <v>-3.028</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.542800000000001</v>
+        <v>-4.3208</v>
       </c>
       <c r="J23" t="n">
-        <v>4.0074</v>
+        <v>19.3135</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3459</v>
+        <v>17.1217</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6616</v>
+        <v>2.1917</v>
       </c>
       <c r="M23" t="n">
-        <v>-22.6596</v>
+        <v>-26.6621</v>
       </c>
       <c r="N23" t="n">
-        <v>-18.4555</v>
+        <v>-20.1495</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.204</v>
+        <v>-6.512700000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1991</v>
+        <v>-5.131499999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-27.6721</v>
+        <v>-36.285</v>
       </c>
       <c r="R23" t="n">
-        <v>25.4727</v>
+        <v>31.1536</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.9095</v>
+        <v>1.4632</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.781</v>
+        <v>1.8249</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.1288</v>
+        <v>-0.3612999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8578</v>
+        <v>-14.3395</v>
       </c>
       <c r="W23" t="n">
-        <v>11.2265</v>
+        <v>-0.7993999999999997</v>
       </c>
       <c r="X23" t="n">
-        <v>-14.0843</v>
+        <v>-13.5401</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>-129.6906</v>
+        <v>-103.6684</v>
       </c>
       <c r="E24" t="n">
-        <v>44.2424</v>
+        <v>51.6743</v>
       </c>
       <c r="F24" t="n">
-        <v>-173.9341</v>
+        <v>-155.3424</v>
       </c>
       <c r="G24" t="n">
         <v>-118.4843</v>
@@ -2314,7 +2314,7 @@
         <v>-279.0731999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-82.44669999999999</v>
+        <v>-82.44670000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-35.7353</v>
@@ -2326,13 +2326,13 @@
         <v>365.5977999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.018700000000003</v>
+        <v>25.003</v>
       </c>
       <c r="T24" t="n">
-        <v>2.573099999999998</v>
+        <v>10.006</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.591800000000001</v>
+        <v>14.9991</v>
       </c>
       <c r="V24" t="n">
         <v>25.54789999999999</v>
